--- a/Classroom Challenge Projects/Faculty Resources/Evaluation Rubric Template.xlsx
+++ b/Classroom Challenge Projects/Faculty Resources/Evaluation Rubric Template.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mathworks-my.sharepoint.com/personal/kathyz_mathworks_com/Documents/Documents/Bridge or Transfer Programs/Student Challenge Projects - Expansion/Classroom Challenge Projects/Instructor Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F90031C-718E-2E4D-ABF0-348D63CF00F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{1F90031C-718E-2E4D-ABF0-348D63CF00F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C9516E0-CA78-F548-BE1E-B85234E9CB24}"/>
   <bookViews>
-    <workbookView xWindow="38060" yWindow="3200" windowWidth="27640" windowHeight="16840" xr2:uid="{0EEB75FC-EC42-7848-B252-A58717A7A485}"/>
+    <workbookView xWindow="23320" yWindow="500" windowWidth="27880" windowHeight="23440" xr2:uid="{0EEB75FC-EC42-7848-B252-A58717A7A485}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>Project Rubric (100 points) - Fillable</t>
   </si>
@@ -77,12 +77,6 @@
     <t>Analysis, Validation &amp; Sanity Checks</t>
   </si>
   <si>
-    <t>Code Quality, Reproducibility &amp; Data</t>
-  </si>
-  <si>
-    <t>Visualization &amp; Communication</t>
-  </si>
-  <si>
     <t>Results, Interpretations &amp; Recommendations</t>
   </si>
   <si>
@@ -90,13 +84,520 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <r>
+      <t>Excellent (9–10):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Clearly states problem, objectives, constraints, and success criteria; explicitly maps tasks to deliverables </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient (7–8):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Objectives and constraints are identified; minor gaps in success criteria or deliverable mapping.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Developing (4–6):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Problem statement is partial; constraints/criteria not well defined; some deliverables unclear.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insufficient (0–3):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Unclear objective; requirements not addressed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Technical Modeling &amp; Correctness (25 pts)</t>
+  </si>
+  <si>
+    <t>Assess mathematical formulation, implementation, and correctness relative to each project’s core methods.</t>
+  </si>
+  <si>
+    <r>
+      <t>Excellent (22–25):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> ____________________________________________ (instructor defines according to project specifics)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient (18–21):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Minor formulation or implementation errors that don’t change conclusions; sound parameter choices; units mostly consistent.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Developing (12–17):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Noticeable errors (e.g., sign mistakes, unit inconsistencies, missing constraints) that weaken conclusions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insufficient (0–11):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Fundamental modeling errors; model not executable or not aligned with physical/optimization principles.</t>
+    </r>
+  </si>
+  <si>
+    <t>Problem Framing &amp; Requirements (10 pts)</t>
+  </si>
+  <si>
+    <t>Analysis, Validation &amp; Sanity Checks (20 pts)</t>
+  </si>
+  <si>
+    <t>Look for triangulation: hand calculations vs. simulation; sensitivity; bounds/edge cases.</t>
+  </si>
+  <si>
+    <r>
+      <t>Excellent (18–20):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compares </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>hand calculations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> with MATLAB results; explores </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>sensitivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">; checks </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>bounds/edge cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Quantifies uncertainty or error and explains discrepancies.</t>
+  </si>
+  <si>
+    <r>
+      <t>o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>____________________________________________ (instructor defines according to project specifics)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient (14–17):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Includes basic cross‑checks; touches on sensitivity or edge cases; provides plausible error discussion.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Developing (9–13):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Minimal cross‑checks; limited sensitivity analysis; inconsistencies not explained.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insufficient (0–8):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> No validation; results taken at face value.</t>
+    </r>
+  </si>
+  <si>
+    <t>Code Quality, Reproducibility, &amp; Documentation (15 pts)</t>
+  </si>
+  <si>
+    <t>Evaluate repository organization, documentation, and ability to re‑run.</t>
+  </si>
+  <si>
+    <r>
+      <t>Excellent (14–15):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Clear file organization; README with setup/run steps (if using); code comments; parameters/data documented; figures regenerate from scripts.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient (11–13):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Mostly organized; README present (if using); minor gaps (e.g., missing figure regeneration step).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Developing (7–10):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Disorganized; sparse documentation; partial reproducibility (manual steps required).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insufficient (0–6):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Hard to run; missing essential files; no documentation.</t>
+    </r>
+  </si>
+  <si>
+    <t>Communicating Project Findings (10 pts)</t>
+  </si>
+  <si>
+    <t>Consider clarity, correctness, and narrative in report/presentation.</t>
+  </si>
+  <si>
+    <r>
+      <t>Excellent (9–10):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> High quality visuals; labeled axes/units; captions link visuals to conclusions; clear, concise writing; logical slide deck.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient (7–8):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Good visuals; minor labeling or narrative gaps.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Developing (4–6):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Basic visuals; cluttered or under labeled; narrative hard to follow.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insufficient (0–3):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Visuals missing or misleading; unclear writing/presentation.</t>
+    </r>
+  </si>
+  <si>
+    <t>Code Quality, Reproducibility &amp; Documentation</t>
+  </si>
+  <si>
+    <t>Communicating Project Findings</t>
+  </si>
+  <si>
+    <t>Results, Interpretation &amp; Recommendations (10 pts)</t>
+  </si>
+  <si>
+    <t>Judge whether conclusions are supported and actionable.</t>
+  </si>
+  <si>
+    <r>
+      <t>Excellent (9–10):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Results summarized with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>; interprets physical/engineering meaning; offers practical next steps/limitations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient (7–8):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Conclusions mostly supported; some limitations acknowledged; actionable suggestions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Developing (4–6):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Over‑generalized claims; limited linkage to evidence; few or no recommendations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insufficient (0–3):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Unsupported conclusions; misinterpretation of results.</t>
+    </r>
+  </si>
+  <si>
+    <t>Teamwork &amp; Collaboration (10 pts)</t>
+  </si>
+  <si>
+    <t>Observe process, equity, and professionalism throughout the project.</t>
+  </si>
+  <si>
+    <r>
+      <t>Excellent (9–10):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Clear role assignment; consistent meeting cadence; responsive communication; equitable workload; constructive peer review; resolves conflicts professionally; timely delivery.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient (7–8):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Roles mostly clear; regular updates; minor unevenness in workload or responsiveness.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Developing (4–6):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Irregular communication; uneven contribution; limited peer review.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insufficient (0–3):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> Poor collaboration; chronic missed deadlines; unresolved conflict; one-person project.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -110,6 +611,35 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -155,6 +685,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="12"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48072439-A033-6E41-828E-4C8664FEDF61}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.33203125" customWidth="1"/>
@@ -574,7 +1119,7 @@
     </row>
     <row r="13" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B13" s="4">
         <v>15</v>
@@ -584,7 +1129,7 @@
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B14" s="4">
         <v>10</v>
@@ -594,7 +1139,7 @@
     </row>
     <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4">
         <v>10</v>
@@ -604,7 +1149,7 @@
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4">
         <v>10</v>
@@ -612,15 +1157,214 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
         <v>100</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2">
+        <f>SUM(C10:C16)</f>
+        <v>0</v>
+      </c>
       <c r="D17" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H26" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H33" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H43" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
